--- a/Result/profitability/5386.xlsx
+++ b/Result/profitability/5386.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.9</v>
       </c>
       <c r="M2" t="n">
-        <v>6.645</v>
+        <v>8.373749999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>9.946250000000001</v>
+        <v>11.99125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>6.47125</v>
+        <v>8.02</v>
       </c>
       <c r="N3" t="n">
-        <v>9.68</v>
+        <v>11.14</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>6.187499999999999</v>
+        <v>7.806249999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.590000000000002</v>
+        <v>10.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5.678749999999999</v>
+        <v>7.29625</v>
       </c>
       <c r="N5" t="n">
-        <v>4.870000000000001</v>
+        <v>6.051250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3425</v>
+        <v>7.038749999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9350000000000005</v>
+        <v>2.640000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>5.181249999999999</v>
+        <v>6.26</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2912500000000005</v>
+        <v>1.07125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4925</v>
+        <v>0.8887500000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4899999999999995</v>
+        <v>-1.4225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5386</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6534</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5251</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1283</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-59</v>
+      </c>
+      <c r="J75" t="n">
+        <v>965</v>
+      </c>
+      <c r="K75" t="n">
+        <v>770</v>
+      </c>
+      <c r="L75" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.535</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.81125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-28.83</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6696864111498257</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.460000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2752767527675277</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.109375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.450000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.927379784102061</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
